--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 59 clubs short</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1364,8 +1364,8 @@
       <c r="P7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="9" t="n">
-        <v>1</v>
+      <c r="Q7" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R7" s="9" t="n">
         <v>0</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>1</v>
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="U37" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V37" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6920,8 +6920,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8569,8 +8569,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -13741,7 +13741,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13972,7 +13972,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14104,7 +14104,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14203,7 +14203,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 59 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -2089,15 +2089,15 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>497</v>
+        <v>7262</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Westlake Toastmasters #497</t>
+          <t>Top-Notch Weekend Toastmasters</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2147,22 +2147,22 @@
         <v>0</v>
       </c>
       <c r="S15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2186,15 +2186,15 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7262</v>
+        <v>497</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Westside Advanced Club</t>
+          <t>Westlake Toastmasters #497</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2244,22 +2244,22 @@
         <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X16" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4204,8 +4204,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4592,8 +4592,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9733,8 +9733,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="S106" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T106" s="10" t="n">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>5</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12158,8 +12158,8 @@
       <c r="Y118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z118" s="9" t="n">
-        <v>0</v>
+      <c r="Z118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA118" s="10" t="n">
         <v>1</v>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="10" t="n">
         <v>2</v>
@@ -13774,7 +13774,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13939,7 +13939,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14170,7 +14170,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14302,7 +14302,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14467,7 +14467,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 52 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -982,8 +982,8 @@
       <c r="R3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="9" t="n">
-        <v>0</v>
+      <c r="S3" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="T3" s="9" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1100,8 +1100,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1488,8 +1488,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1682,8 +1682,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2458,8 +2458,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2555,8 +2555,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2928,8 +2928,8 @@
       <c r="T23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
+      <c r="U23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>0</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3310,8 +3310,8 @@
       <c r="R27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="9" t="n">
-        <v>1</v>
+      <c r="S27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T27" s="9" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3816,8 +3816,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3913,8 +3913,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="10" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4010,8 +4010,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4689,8 +4689,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" s="10" t="n">
         <v>7</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5465,8 +5465,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6241,8 +6241,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8957,8 +8957,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9442,8 +9442,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="10" t="n">
         <v>2</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10897,8 +10897,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12352,8 +12352,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="9" t="n">
         <v>0</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12619,8 +12619,8 @@
       <c r="Q123" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R123" s="9" t="n">
-        <v>1</v>
+      <c r="R123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S123" s="10" t="n">
         <v>4</v>
@@ -12735,7 +12735,7 @@
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13058,7 +13058,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13113,8 +13113,8 @@
       <c r="T128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V128" s="9" t="n">
         <v>1</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13220,13 +13220,13 @@
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13613,8 +13613,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13708,7 +13708,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -13774,7 +13774,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13840,7 +13840,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13873,7 +13873,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -13939,7 +13939,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14005,7 +14005,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14038,7 +14038,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14203,7 +14203,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14236,7 +14236,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -14269,7 +14269,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14302,7 +14302,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14368,7 +14368,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14533,7 +14533,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -14566,7 +14566,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>1</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1771,7 +1771,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>7</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2052,14 +2052,14 @@
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3022,8 +3022,8 @@
       <c r="S24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
+      <c r="T24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U24" s="9" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3222,8 +3222,8 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3319,8 +3319,8 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>1</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4671,8 +4671,8 @@
       <c r="S41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T41" s="9" t="n">
-        <v>0</v>
+      <c r="T41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U41" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4768,8 +4768,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5147,14 +5147,14 @@
       <c r="P46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" s="9" t="n">
-        <v>1</v>
+      <c r="Q46" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T46" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="8" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" s="9" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5938,8 +5938,8 @@
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="9" t="n">
-        <v>2</v>
+      <c r="V54" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5991,17 +5991,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6130,13 +6130,13 @@
         <v>1</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V56" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>6</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6670,17 +6670,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q67" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
         <v>4</v>
       </c>
       <c r="W67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X67" s="10" t="n">
         <v>5</v>
@@ -7252,17 +7252,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7640,17 +7640,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8169,8 +8169,8 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>3</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8222,17 +8222,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>4</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>5</v>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -9624,11 +9624,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>2</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>4</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10303,8 +10303,8 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>2</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>7</v>
+        <v>-15</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -10985,8 +10985,8 @@
       <c r="V106" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W106" s="9" t="n">
-        <v>3</v>
+      <c r="W106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>5</v>
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12199,17 +12199,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,17 +12393,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -12808,7 +12808,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12922,8 +12922,8 @@
       <c r="U126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>2</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13363,17 +13363,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13774,7 +13774,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -13789,7 +13789,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13840,7 +13840,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13939,7 +13939,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -13954,7 +13954,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -13972,7 +13972,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14020,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -14038,7 +14038,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14053,7 +14053,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14086,7 +14086,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -14104,7 +14104,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -14152,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14170,7 +14170,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14218,7 +14218,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -14284,7 +14284,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -14302,13 +14302,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -14335,7 +14335,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14350,7 +14350,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14401,13 +14401,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -14416,7 +14416,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -14449,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -14482,7 +14482,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -14515,7 +14515,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -14533,13 +14533,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -14581,7 +14581,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="10" t="n">
         <v>2</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2343,8 +2343,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="10" t="n">
         <v>2</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6714,8 +6714,8 @@
       <c r="U62" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7678,8 +7678,8 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8751,8 +8751,8 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>3</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>3</v>
       </c>
       <c r="S92" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="10" t="n">
         <v>6</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10400,8 +10400,8 @@
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>3</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>4</v>
       </c>
       <c r="W106" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>5</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11547,10 +11547,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>1</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13774,7 +13774,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -14071,7 +14071,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14137,7 +14137,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14236,7 +14236,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -14335,7 +14335,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/docs/d/219/inyear.xlsx
+++ b/docs/d/219/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
@@ -2208,17 +2208,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3472,10 +3472,10 @@
         <v>13</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5162,11 +5162,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -5606,10 +5606,10 @@
         <v>21</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6326,8 +6326,8 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>3</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7005,8 +7005,8 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>3</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8066,8 +8066,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -8640,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" s="10" t="n">
         <v>1</v>
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>1</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10068,10 +10068,10 @@
         <v>12</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12520,16 +12520,16 @@
         <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X126" s="10" t="n">
         <v>7</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M128" s="8" t="n">
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13207,8 +13207,8 @@
       <c r="S129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13789,7 +13789,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -13972,7 +13972,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14038,7 +14038,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14104,7 +14104,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14170,7 +14170,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14500,7 +14500,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -14548,7 +14548,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -14566,7 +14566,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
